--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_33.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_33.xlsx
@@ -471,45 +471,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1597</v>
+        <v>68346</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Benjamin Sales</t>
+          <t>Davi Lucas Cardoso</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>45099</v>
       </c>
       <c r="G2" t="n">
-        <v>6890.11</v>
+        <v>7622.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>92439</v>
+        <v>53391</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vitor Hugo Lopes</t>
+          <t>Dra. Alexia Dias</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -518,27 +518,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45080</v>
+        <v>45093</v>
       </c>
       <c r="G3" t="n">
-        <v>6867.66</v>
+        <v>7962.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>23149</v>
+        <v>16172</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Isadora Freitas</t>
+          <t>Larissa Rodrigues</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,85 +547,85 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45080</v>
+        <v>45100</v>
       </c>
       <c r="G4" t="n">
-        <v>12157.35</v>
+        <v>12112.28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>72552</v>
+        <v>15009</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lavínia Almeida</t>
+          <t>Ana Beatriz Cavalcanti</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Recursos Humanos</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45095</v>
+        <v>45080</v>
       </c>
       <c r="G5" t="n">
-        <v>2869.43</v>
+        <v>8643.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>80472</v>
+        <v>73487</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dr. Lucas Gabriel Sales</t>
+          <t>Danilo Monteiro</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45105</v>
+        <v>45101</v>
       </c>
       <c r="G6" t="n">
-        <v>9797.790000000001</v>
+        <v>8039.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57677</v>
+        <v>13707</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maria Luiza da Conceição</t>
+          <t>Srta. Larissa Martins</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -637,48 +637,48 @@
         <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45085</v>
+        <v>45094</v>
       </c>
       <c r="G7" t="n">
-        <v>9632.76</v>
+        <v>4411.46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3416</v>
+        <v>73735</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dra. Ana Luiza Monteiro</t>
+          <t>Otávio Vieira</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45098</v>
+        <v>45106</v>
       </c>
       <c r="G8" t="n">
-        <v>8688.629999999999</v>
+        <v>10674.74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>39979</v>
+        <v>62047</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Alana Pires</t>
+          <t>Raquel Moraes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -688,75 +688,75 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Viagem de negócios</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45101</v>
+        <v>45079</v>
       </c>
       <c r="G9" t="n">
-        <v>6912.3</v>
+        <v>5208.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89735</v>
+        <v>89518</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Gabriela Souza</t>
+          <t>Dr. Vinicius Campos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45101</v>
+        <v>45089</v>
       </c>
       <c r="G10" t="n">
-        <v>5281.64</v>
+        <v>10933.78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>39492</v>
+        <v>87273</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Marcela Melo</t>
+          <t>Noah da Costa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Operações</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Outros</t>
         </is>
       </c>
       <c r="E11" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45089</v>
+        <v>45084</v>
       </c>
       <c r="G11" t="n">
-        <v>8772.889999999999</v>
+        <v>10973.39</v>
       </c>
     </row>
   </sheetData>
